--- a/Result/profitability/2324.xlsx
+++ b/Result/profitability/2324.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.84</v>
       </c>
       <c r="M2" t="n">
-        <v>0.485</v>
+        <v>0.48</v>
       </c>
       <c r="N2" t="n">
-        <v>5.5625</v>
+        <v>5.513750000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.83</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4925</v>
+        <v>0.5287500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>5.859999999999999</v>
+        <v>5.807499999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.89</v>
       </c>
       <c r="M4" t="n">
-        <v>0.54875</v>
+        <v>0.5775</v>
       </c>
       <c r="N4" t="n">
-        <v>6.11375</v>
+        <v>6.035</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.71</v>
       </c>
       <c r="M5" t="n">
-        <v>0.575</v>
+        <v>0.6525</v>
       </c>
       <c r="N5" t="n">
-        <v>6.33625</v>
+        <v>6.18</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.73</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6525</v>
+        <v>0.6875</v>
       </c>
       <c r="N6" t="n">
-        <v>6.405</v>
+        <v>6.27375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.84</v>
       </c>
       <c r="M7" t="n">
-        <v>0.70125</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>6.495</v>
+        <v>6.345</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.33</v>
       </c>
       <c r="M8" t="n">
-        <v>0.8275</v>
+        <v>0.8625</v>
       </c>
       <c r="N8" t="n">
-        <v>6.543749999999999</v>
+        <v>6.46375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1648,7 +1648,7 @@
         <v>1.17875</v>
       </c>
       <c r="N10" t="n">
-        <v>6.4625</v>
+        <v>6.462499999999999</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2324</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>238295</v>
+      </c>
+      <c r="D75" t="n">
+        <v>227274</v>
+      </c>
+      <c r="E75" t="n">
+        <v>11021</v>
+      </c>
+      <c r="F75" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="G75" t="n">
+        <v>2855</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>1.20%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>1785</v>
+      </c>
+      <c r="J75" t="n">
+        <v>4639</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3133</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.47125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>5.3175</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6222222222222222</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.6399999999999997</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.1216730038022813</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>5.636363636363636</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2129471890971039</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
